--- a/db/Insurance_Support_Agent_Seed_Data.xlsx
+++ b/db/Insurance_Support_Agent_Seed_Data.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policies" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Billing" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Policies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Billing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Claims" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15,9 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -469,12 +468,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Kumar Thiagarajan</t>
+          <t>Alex Carter</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>kumar.t@xyz.com</t>
+          <t>alex.c@xyz.com</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
